--- a/output/materials_equipment.xlsx
+++ b/output/materials_equipment.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jadval'!$A$1:$E$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manbalar'!$A$1:$I$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manbalar'!$A$1:$I$272</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Identifikatsiya'!$A$1:$K$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
         <is>
           <t>M01_CHEMFOS_740R_brochure_EQUIV.pdf (yuklanmagan)
 M01_CHEMFOS_740R_TDS_EQUIV.pdf (yuklanmagan)
-M01_CHEMFOS_740R_TDS_EQUIV_2.pdf (yuklanmagan)</t>
+[veb-sahifa, PDF emas] https://www.ppg.com/en-US/autocoatings/products/pretreatment</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -512,8 +512,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>M02_ED7010_Binder_Gray_brochure_EQUIV.pdf (yuklanmagan)
-M02_ED7010_Binder_Gray_brochure_EQUIV_2.pdf (yuklanmagan)</t>
+          <t>[veb-sahifa, PDF emas] https://www.ppg.com/autocoatings/en-US/products/electrocoat
+[veb-sahifa, PDF emas] https://www.kccworld.co.kr/eng/paints/automotive.do</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf (yuklanmagan)
+          <t>EQ_Durr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf (yuklanmagan)
 EQ_Controlled_Power_Com_AACD_Series_50_e_coat_rectifier_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
@@ -542,8 +542,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>M03_ED7010_Paste_Gray_brochure_EQUIV.pdf (yuklanmagan)
-M03_ED7010_Paste_Gray_brochure_EQUIV_2.pdf (yuklanmagan)</t>
+          <t>[veb-sahifa, PDF emas] https://www.ppg.com/autocoatings/en-US/products/electrocoat
+[veb-sahifa, PDF emas] https://www.kccworld.co.kr/eng/paints/automotive.do</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf (yuklanmagan)
+          <t>EQ_Durr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf (yuklanmagan)
 EQ_Controlled_Power_Com_AACD_Series_50_e_coat_rectifier_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
@@ -586,8 +586,8 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>EQ_Graco_E_Flo_SP_supply_systems_manual.pdf (yuklanmagan)
-EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf (yuklanmagan)
-EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
+EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf (yuklanmagan)
+EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
 EQ_Graco_PrecisionFlo_XL_manual.pdf (yuklanmagan)
 EQ_Atlas_Copco_SCA_SCA_dosing_pocket_guide_brochure.pdf (yuklanmagan)</t>
         </is>
@@ -605,8 +605,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>M05_UBC_UNDER_COAT_RSU_230_SDS_EQUIV.pdf (yuklanmagan)
-M05_UBC_UNDER_COAT_RSU_230_brochure_EQUIV.pdf (yuklanmagan)</t>
+          <t>[veb-sahifa, PDF emas] https://nextsds.com/sds/en/281331501310308/teroson-pv-3011-us-1-so-sb-dr187kg
+[veb-sahifa, PDF emas] https://automotive.sika.com/en/solution-products/paint-shop-sealants/underbody-coating.html</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -614,14 +614,15 @@
           <t>Graco E-Flo SP electric supply system (D200/D200S 200 L drum ram) or Check-Mate/Dura-Flo ram — Drum unloading / supply pump for high-viscosity PVC plastisol from 200-250 kg drums [medium]
 Dürr EcoShotMeter (piston dosing) + EcoGun2 3D applicator on sealing robot (EcoRP) — Volumetric dosing and robotic bead/flat-stream application of seam sealer / UBC [medium]
 Atlas Copco (SCA) SCA paint shop dispensing system (ASC 5000 controller, dosing units) — Alternative dosing/controller for paint-shop sealing &amp; dampening [low]
-Graco PrecisionFlo XL — Alternative electronically controlled sealant metering/dispense package [low]</t>
+Graco PrecisionFlo XL — Alternative electronically controlled sealant metering/dispense package [low]
+Graco / Dürr Robotic airless / flat-stream spray package (e.g. Graco King airless pump + robot airless gun) — PVC underbody / anti-chip spray application [low]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>EQ_Graco_E_Flo_SP_supply_systems_manual.pdf (yuklanmagan)
-EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf (yuklanmagan)
-EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
+EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf (yuklanmagan)
+EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
 EQ_Graco_PrecisionFlo_XL_manual.pdf (yuklanmagan)
 EQ_Atlas_Copco_SCA_SCA_dosing_pocket_guide_brochure.pdf (yuklanmagan)</t>
         </is>
@@ -639,7 +640,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M06_UBS_COAT_SDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>[veb-sahifa, PDF emas] https://nextsds.com/sds/en/281331501309209/teroson-pv-3146-ab-oa-sb-to1400kg</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -647,14 +648,15 @@
           <t>Graco E-Flo SP electric supply system (D200/D200S 200 L drum ram) or Check-Mate/Dura-Flo ram — Drum unloading / supply pump for high-viscosity PVC plastisol from 200-250 kg drums [medium]
 Dürr EcoShotMeter (piston dosing) + EcoGun2 3D applicator on sealing robot (EcoRP) — Volumetric dosing and robotic bead/flat-stream application of seam sealer / UBC [medium]
 Atlas Copco (SCA) SCA paint shop dispensing system (ASC 5000 controller, dosing units) — Alternative dosing/controller for paint-shop sealing &amp; dampening [low]
-Graco PrecisionFlo XL — Alternative electronically controlled sealant metering/dispense package [low]</t>
+Graco PrecisionFlo XL — Alternative electronically controlled sealant metering/dispense package [low]
+Graco / Dürr Robotic airless / flat-stream spray package (e.g. Graco King airless pump + robot airless gun) — PVC underbody / anti-chip spray application [low]</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>EQ_Graco_E_Flo_SP_supply_systems_manual.pdf (yuklanmagan)
-EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf (yuklanmagan)
-EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
+EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf (yuklanmagan)
+EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
 EQ_Graco_PrecisionFlo_XL_manual.pdf (yuklanmagan)
 EQ_Atlas_Copco_SCA_SCA_dosing_pocket_guide_brochure.pdf (yuklanmagan)</t>
         </is>
@@ -672,8 +674,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>M07_PVC_ANTI_CHIP_brochure_EQUIV.pdf (yuklanmagan)
-M07_PVC_ANTI_CHIP_PDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>[veb-sahifa, PDF emas] https://automotive.sika.com/en/solution-products/paint-shop-sealants/underbody-coating.html</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -681,14 +682,15 @@
           <t>Graco E-Flo SP electric supply system (D200/D200S 200 L drum ram) or Check-Mate/Dura-Flo ram — Drum unloading / supply pump for high-viscosity PVC plastisol from 200-250 kg drums [medium]
 Dürr EcoShotMeter (piston dosing) + EcoGun2 3D applicator on sealing robot (EcoRP) — Volumetric dosing and robotic bead/flat-stream application of seam sealer / UBC [medium]
 Atlas Copco (SCA) SCA paint shop dispensing system (ASC 5000 controller, dosing units) — Alternative dosing/controller for paint-shop sealing &amp; dampening [low]
-Graco PrecisionFlo XL — Alternative electronically controlled sealant metering/dispense package [low]</t>
+Graco PrecisionFlo XL — Alternative electronically controlled sealant metering/dispense package [low]
+Graco / Dürr Robotic airless / flat-stream spray package (e.g. Graco King airless pump + robot airless gun) — PVC underbody / anti-chip spray application [low]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>EQ_Graco_E_Flo_SP_supply_systems_manual.pdf (yuklanmagan)
-EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf (yuklanmagan)
-EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
+EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf (yuklanmagan)
+EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf (yuklanmagan)
 EQ_Graco_PrecisionFlo_XL_manual.pdf (yuklanmagan)
 EQ_Atlas_Copco_SCA_SCA_dosing_pocket_guide_brochure.pdf (yuklanmagan)</t>
         </is>
@@ -719,13 +721,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoRP_E043i_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
+          <t>EQ_Durr_EcoRP_E043i_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
 EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
+EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -741,7 +743,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>M09_CR_100_PRIMER_SURFACER_PURE_WHITE_N9_0_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M08_CR_100_PRIMER_SURFACER_LIGHT_GRAY_N7_0_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -754,13 +756,13 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoRP_E043i_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
+          <t>EQ_Durr_EcoRP_E043i_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
 EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
+EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -787,8 +789,8 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -820,14 +822,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -843,8 +845,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>M12_GK2_BASE_COAT_SON_OF_A_GUN_GRAY_MET_3_SDS_EQUIV.pdf (yuklanmagan)
-M12_GK2_BASE_COAT_SON_OF_A_GUN_GRAY_MET_3_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -859,14 +861,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -882,8 +884,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>M13_GD8_BASE_COAT_BURNT_COCONUTMET_SDS_EQUIV.pdf (yuklanmagan)
-M13_GD8_BASE_COAT_BURNT_COCONUTMET_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -898,14 +900,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -921,8 +923,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>M14_GBO_BASE_COAT_BLACK_MEET_KETTLE_MET_3_SDS_EQUIV.pdf (yuklanmagan)
-M14_GBO_BASE_COAT_BLACK_MEET_KETTLE_MET_3_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -937,14 +939,14 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -960,8 +962,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>M15_GYM_BASE_COAT_SATIN_STEEL_GRAYMET_SDS_EQUIV.pdf (yuklanmagan)
-M15_GYM_BASE_COAT_SATIN_STEEL_GRAYMET_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -976,14 +978,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -999,8 +1001,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>M16_GAN_BASE_COAT_SWITCHBLADE_SILVER_SDS_EQUIV.pdf (yuklanmagan)
-M16_GAN_BASE_COAT_SWITCHBLADE_SILVER_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1015,14 +1017,14 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1038,8 +1040,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>M17_GL8_BASE_COAT_RED_E_OR_NOT_RED_MET_3_SDS_EQUIV.pdf (yuklanmagan)
-M17_GL8_BASE_COAT_RED_E_OR_NOT_RED_MET_3_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1054,14 +1056,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1077,8 +1079,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>M18_GUM_BASE_COAT_SEEKER_MET_3_SDS_EQUIV.pdf (yuklanmagan)
-M18_GUM_BASE_COAT_SEEKER_MET_3_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1093,14 +1095,14 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1116,8 +1118,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>M19_G7G_BASE_COAT_ZEUS_SDS_EQUIV.pdf (yuklanmagan)
-M19_G7G_BASE_COAT_ZEUS_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1132,14 +1134,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1155,8 +1157,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>M20_GZ8_BASE_COAT_SOME_KINDA_BLUE_SDS_EQUIV.pdf (yuklanmagan)
-M20_GZ8_BASE_COAT_SOME_KINDA_BLUE_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1171,14 +1173,14 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1194,8 +1196,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>M21_G5J_BASE_COAT_DARKMOON_BLUE_SDS_EQUIV.pdf (yuklanmagan)
-M21_G5J_BASE_COAT_DARKMOON_BLUE_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1210,14 +1212,14 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1233,8 +1235,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>M22_G4V_BASE_COAT_POW_ZINGA_MET_3_SDS_EQUIV.pdf (yuklanmagan)
-M22_G4V_BASE_COAT_POW_ZINGA_MET_3_TDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf (yuklanmagan)
+M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1249,14 +1251,14 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf (yuklanmagan)
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
-EQ_ABB_RB1000i_series_brochure.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply_P_brochure.pdf (yuklanmagan)
+EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoMCC3_20_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply_P_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_15_datasheet.pdf (yuklanmagan)
-EQ_FANUC_P_250iB_brochure.pdf (yuklanmagan)</t>
+EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1283,8 +1285,8 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1302,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>M24_TOP_CLEAR_HITEC_2000_brochure_EQUIV.pdf (yuklanmagan)
+          <t>[veb-sahifa, PDF emas] https://www.ppg.com/en-US/autocoatings/products/clearcoats
 M24_TOP_CLEAR_HITEC_2000_TDS_EQUIV.pdf (yuklanmagan)</t>
         </is>
       </c>
@@ -1314,13 +1316,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoRP_E043i_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
+          <t>EQ_Durr_EcoRP_E043i_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_FlexPainter_brochure.pdf (yuklanmagan)
 EQ_ABB_IRB_5500_22_datasheet.pdf (yuklanmagan)
 EQ_ABB_RB1000i_brochure.pdf (yuklanmagan)
 EQ_FANUC_P_250iB_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
+EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1348,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1373,9 +1375,9 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell_Cleaner_D2_EcoBell_PurgeBox_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoBell3_datasheet.pdf (yuklanmagan)
-EQ_D_rr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_EcoBell_Cleaner_D2_EcoBell_PurgeBox_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoBell3_datasheet.pdf (yuklanmagan)
+EQ_Durr_EcoSupply2_Core_datasheet.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1402,9 +1404,9 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1433,9 +1435,9 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1463,9 +1465,9 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1491,9 +1493,9 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1511,8 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>M31_T_M_OIL_MANUAL_SH_XGP_75W85_GL_4_PDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M31_T_M_OIL_MANUAL_SH_XGP_75W85_GL_4_PDS_EQUIV.pdf (yuklanmagan)
+[veb-sahifa, PDF emas] https://parts.gmparts.com/product/acdelco-gm-original-equipment-xgp-sae-75w-85-manual-transmission-fluid-1-qt-19351859</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1519,9 +1522,9 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1537,10 +1540,10 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>M32_A_T_OIL_DEXRON_VI_TDS_EQUIV.pdf (yuklanmagan)
-M32_A_T_OIL_DEXRON_VI_TDS_EQUIV_2.pdf (yuklanmagan)
-M32_A_T_OIL_DEXRON_VI_SDS_EQUIV.pdf (yuklanmagan)
-M32_A_T_OIL_DEXRON_VI_SDS_EQUIV_2.pdf (yuklanmagan)</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV.pdf (yuklanmagan)
+M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV_2.pdf (yuklanmagan)
+M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV.pdf (yuklanmagan)
+M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV_2.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1550,9 +1553,9 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1581,10 +1584,9 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_Somac_filling_stations_refrigerant_proce_manual.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1602,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>M34_FUEL_standard_EQUIV.pdf (yuklanmagan)
+          <t>[veb-sahifa, PDF emas] https://meganorm.ru/mega_doc/norm/gost_gosudarstvennyj-standart/20/gost_32513-2013_mezhgosudarstvennyy_standart_topliva.html
 M34_FUEL_SDS_EQUIV.pdf (yuklanmagan)
 M34_FUEL_SDS_EQUIV_2.pdf (yuklanmagan)</t>
         </is>
@@ -1612,9 +1614,9 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1641,9 +1643,9 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
-EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf (yuklanmagan)
+EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf (yuklanmagan)</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1815,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>M41_RAD_11724_PDS_EQUIV.pdf (yuklanmagan)</t>
+          <t>M40_BETAPRIME_PDS.pdf (yuklanmagan)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1867,8 +1869,8 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>M43_LUBRICANT_CLU_PLT_HUB_M_T_PDS.pdf (yuklanmagan)
-M43_LUBRICANT_CLU_PLT_HUB_M_T_PDS_2.pdf (yuklanmagan)</t>
+          <t>[veb-sahifa, PDF emas] https://www.klueber.com/us/en/products-service/products/microlube-gny-202/9866/
+[veb-sahifa, PDF emas] https://klueber.com/uk/en/products-service/products/microlube-gny-202/9866</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1895,7 +1897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2057,17 +2059,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Material: brochure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>M01_CHEMFOS_740R_TDS_EQUIV_2.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://datasheets.globalspec.com/ds/ppg-industries/chemfos-ka/e98a892a-e888-4e62-ba8b-177307e1c5ec</t>
+          <t>https://www.ppg.com/en-US/autocoatings/products/pretreatment</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2082,12 +2084,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Web page, not PDF. Iron phosphate for general industry - confirms CHEMFOS brand but NOT a functional equivalent of automotive zinc phosphate.</t>
+          <t>HTML product page (brand/process confirmation)</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2109,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf</t>
+          <t>EQ_Durr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2132,7 +2134,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Path suggests PT/EC bath-cleaning/wet-system brochure; RoDip described per search summary.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Path suggests PT/EC bath-cleaning/wet-system brochure; RoDip described per search summary. Reviewer: general Ecopaint WetSystem PT/ED brochure, not RoDip-specific.</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2154,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>M02_ED7010_Binder_Gray_brochure_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2172,7 +2174,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2197,7 +2199,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>M02_ED7010_Binder_Gray_brochure_EQUIV_2.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2217,7 +2219,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2242,7 +2244,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf</t>
+          <t>EQ_Durr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2332,7 +2334,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>M03_ED7010_Paste_Gray_brochure_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2352,7 +2354,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2377,7 +2379,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>M03_ED7010_Paste_Gray_brochure_EQUIV_2.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2397,7 +2399,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2422,7 +2424,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf</t>
+          <t>EQ_Durr_Ecopaint_RoDip_PT_ED_rotary_dip_brochure.pdf</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2602,7 +2604,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf</t>
+          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2647,7 +2649,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
+          <t>EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2672,7 +2674,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Covers EcoShotMeter Tandem piston dosing + EcoMeter SP.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Covers EcoShotMeter Tandem piston dosing + EcoMeter SP. Reviewer: EcoShotMeter Tandem sheet filed under battery gluing - weak match.</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2784,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>M05_UBC_UNDER_COAT_RSU_230_SDS_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2802,7 +2804,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2827,7 +2829,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>M05_UBC_UNDER_COAT_RSU_230_brochure_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2847,7 +2849,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2917,7 +2919,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf</t>
+          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2962,7 +2964,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
+          <t>EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3097,7 +3099,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>M06_UBS_COAT_SDS_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3117,7 +3119,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3187,7 +3189,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf</t>
+          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3232,7 +3234,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
+          <t>EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3367,7 +3369,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>M07_PVC_ANTI_CHIP_brochure_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3387,7 +3389,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -3407,22 +3409,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Jihoz: manual</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>M07_PVC_ANTI_CHIP_PDS_EQUIV.pdf</t>
+          <t>EQ_Graco_E_Flo_SP_supply_systems_manual.pdf</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://usa.sika.com/content/dam/dms/us01/5/pds-ipd-sikagard%206682-US%20final%20%205.6.16.pdf</t>
+          <t>https://gww.graco.com/content/dam/graco/tech_documents/manuals/3A6/3A6331/3A6331EN-L.pdf</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3437,7 +3439,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Anti-chip function equivalent but WATER-BASED (not PVC) - weak equivalent.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index.</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3459,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_E_Flo_SP_supply_systems_manual.pdf</t>
+          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_2.pdf</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://gww.graco.com/content/dam/graco/tech_documents/manuals/3A6/3A6331/3A6331EN-L.pdf</t>
+          <t>https://www.graco.com/content/dam/graco/tech_documents/manuals/3A6/3A6331/3A6853RU-G.pdf</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3482,7 +3484,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Russian translation, useful for plant staff.</t>
         </is>
       </c>
     </row>
@@ -3497,17 +3499,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: manual</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_E_Flo_SP_supply_systems_manual_3A6853RU_G.pdf</t>
+          <t>EQ_Durr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.graco.com/content/dam/graco/tech_documents/manuals/3A6/3A6331/3A6853RU-G.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/05_Sealing_Gluing_Technology/03_Gluing_Application_Technology_Battery_Systems/duerr-datsheet-endless-dosing-en.pdf</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3527,7 +3529,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Russian translation, useful for plant staff.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Covers EcoShotMeter Tandem piston dosing + EcoMeter SP.</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3544,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: manual</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoShotMeter_Tandem_EcoMeter_SP_datasheet.pdf</t>
+          <t>EQ_Graco_PrecisionFlo_XL_manual.pdf</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/05_Sealing_Gluing_Technology/03_Gluing_Application_Technology_Battery_Systems/duerr-datsheet-endless-dosing-en.pdf</t>
+          <t>https://airless.es/manuales/graco/309374r.pdf</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3572,7 +3574,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Covers EcoShotMeter Tandem piston dosing + EcoMeter SP.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Third-party mirror (airless.es), ~2001 revision.</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3589,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: manual</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_PrecisionFlo_XL_manual.pdf</t>
+          <t>EQ_Atlas_Copco_SCA_SCA_dosing_pocket_guide_brochure.pdf</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://airless.es/manuales/graco/309374r.pdf</t>
+          <t>https://shopit.atlascopco.com/content/dam/atlas-copco/industrial-technique/general/documents/pocketguides/Atlas%20Copco-DT-9833%202169%2001-2019DE.pdf</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3617,37 +3619,37 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. Third-party mirror (airless.es), ~2001 revision.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. German; general SCA dosing guide.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PVC ANTI CHIP</t>
+          <t>CR-100 PRIMER SURFACER LIGHT GRAY (N7.0)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>EQ_Atlas_Copco_SCA_SCA_dosing_pocket_guide_brochure.pdf</t>
+          <t>M08_CR_100_PRIMER_SURFACER_LIGHT_GRAY_N7_0_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://shopit.atlascopco.com/content/dam/atlas-copco/industrial-technique/general/documents/pocketguides/Atlas%20Copco-DT-9833%202169%2001-2019DE.pdf</t>
+          <t>https://vrteotgdakjwbjeugnxx.supabase.co/storage/v1/object/public/product-images/datasheets/kcc/KCC_DATASHEET_US4000_eng.pdf</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3662,7 +3664,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only, title from search index. German; general SCA dosing guide.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Third-party hosted copy; refinish product, not OEM line - loose equivalent only.</t>
         </is>
       </c>
     </row>
@@ -3677,22 +3679,22 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>M08_CR_100_PRIMER_SURFACER_LIGHT_GRAY_N7_0_TDS_EQUIV.pdf</t>
+          <t>EQ_Durr_EcoRP_E043i_datasheet.pdf</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://vrteotgdakjwbjeugnxx.supabase.co/storage/v1/object/public/product-images/datasheets/kcc/KCC_DATASHEET_US4000_eng.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/07_Paint_robots/01_Paint_Robots_Automotive/duerr-datasheet-ecorp-e043i-en.pdf</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3707,7 +3709,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Third-party hosted copy; refinish product, not OEM line - loose equivalent only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3729,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoRP_E043i_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/07_Paint_robots/01_Paint_Robots_Automotive/duerr-datasheet-ecorp-e043i-en.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3767,17 +3769,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3812,17 +3814,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3857,17 +3859,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3887,7 +3889,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Presentation incl. data sheet section; no standalone RB1000 datasheet PDF found.</t>
         </is>
       </c>
     </row>
@@ -3902,17 +3904,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3932,7 +3934,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Presentation incl. data sheet section; no standalone RB1000 datasheet PDF found.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3954,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3983,31 +3985,31 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CR-100 PRIMER SURFACER LIGHT GRAY (N7.0)</t>
+          <t>CR-100 PRIMER SURFACER PURE WHITE (N9.0)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>M08_CR_100_PRIMER_SURFACER_LIGHT_GRAY_N7_0_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
+          <t>https://vrteotgdakjwbjeugnxx.supabase.co/storage/v1/object/public/product-images/datasheets/kcc/KCC_DATASHEET_US4000_eng.pdf</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4022,7 +4024,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Third-party hosted copy; refinish product, not OEM line - loose equivalent only.</t>
         </is>
       </c>
     </row>
@@ -4037,22 +4039,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>M09_CR_100_PRIMER_SURFACER_PURE_WHITE_N9_0_TDS_EQUIV.pdf</t>
+          <t>EQ_Durr_EcoRP_E043i_datasheet.pdf</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://vrteotgdakjwbjeugnxx.supabase.co/storage/v1/object/public/product-images/datasheets/kcc/KCC_DATASHEET_US4000_eng.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/07_Paint_robots/01_Paint_Robots_Automotive/duerr-datasheet-ecorp-e043i-en.pdf</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4067,7 +4069,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Third-party hosted copy; refinish product, not OEM line - loose equivalent only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -4087,12 +4089,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoRP_E043i_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/07_Paint_robots/01_Paint_Robots_Automotive/duerr-datasheet-ecorp-e043i-en.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -4127,17 +4129,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4172,17 +4174,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -4217,17 +4219,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -4247,7 +4249,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Presentation incl. data sheet section; no standalone RB1000 datasheet PDF found.</t>
         </is>
       </c>
     </row>
@@ -4262,17 +4264,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4292,7 +4294,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Presentation incl. data sheet section; no standalone RB1000 datasheet PDF found.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4314,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4343,11 +4345,11 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CR-100 PRIMER SURFACER PURE WHITE (N9.0)</t>
+          <t>PRIMER TYPE THINNER</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4357,7 +4359,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4402,12 +4404,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4433,31 +4435,31 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>PRIMER TYPE THINNER</t>
+          <t>(GAZ) BASE COAT SUMMIT WHITE (2C1B)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4472,7 +4474,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -4487,17 +4489,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4517,7 +4519,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -4532,22 +4534,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4562,7 +4564,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4584,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4607,7 +4609,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4624,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4652,7 +4654,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -4667,17 +4669,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4697,7 +4699,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4719,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4742,7 +4744,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -4757,17 +4759,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4787,7 +4789,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -4802,17 +4804,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4832,7 +4834,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4849,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4877,37 +4879,37 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>(GAZ) BASE COAT SUMMIT WHITE (2C1B)</t>
+          <t>(GK2) BASE COAT SON OF A GUN GRAY MET-3</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4922,7 +4924,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -4937,17 +4939,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>M12_GK2_BASE_COAT_SON_OF_A_GUN_GRAY_MET_3_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4967,7 +4969,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -4982,22 +4984,22 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>M12_GK2_BASE_COAT_SON_OF_A_GUN_GRAY_MET_3_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5012,7 +5014,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5034,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -5057,7 +5059,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -5072,17 +5074,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -5102,7 +5104,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -5117,17 +5119,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -5147,7 +5149,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5169,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -5192,7 +5194,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -5207,17 +5209,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5237,7 +5239,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5254,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5282,7 +5284,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -5297,17 +5299,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -5327,37 +5329,37 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>(GK2) BASE COAT SON OF A GUN GRAY MET-3</t>
+          <t>(GD8) BASE COAT BURNT COCONUTMET</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -5372,7 +5374,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -5387,17 +5389,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>M13_GD8_BASE_COAT_BURNT_COCONUTMET_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5417,7 +5419,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -5432,22 +5434,22 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>M13_GD8_BASE_COAT_BURNT_COCONUTMET_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -5462,7 +5464,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5484,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -5507,7 +5509,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -5522,17 +5524,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -5552,7 +5554,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -5567,17 +5569,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5597,7 +5599,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5619,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5642,7 +5644,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -5657,17 +5659,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5687,7 +5689,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -5702,17 +5704,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -5732,7 +5734,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -5747,17 +5749,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5777,37 +5779,37 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>(GD8) BASE COAT BURNT COCONUTMET</t>
+          <t>(GBO) BASE COAT BLACK MEET KETTLE MET-3</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5822,7 +5824,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -5837,17 +5839,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>M14_GBO_BASE_COAT_BLACK_MEET_KETTLE_MET_3_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5867,7 +5869,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -5882,22 +5884,22 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>M14_GBO_BASE_COAT_BLACK_MEET_KETTLE_MET_3_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5912,7 +5914,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -5932,12 +5934,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5957,7 +5959,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -5972,17 +5974,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -6002,7 +6004,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -6017,17 +6019,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -6047,7 +6049,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -6067,12 +6069,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -6092,7 +6094,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -6107,17 +6109,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -6137,7 +6139,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -6152,17 +6154,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -6182,7 +6184,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -6197,17 +6199,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -6227,37 +6229,37 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>(GBO) BASE COAT BLACK MEET KETTLE MET-3</t>
+          <t>(GYM) BASE COAT SATIN STEEL GRAYMET</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -6272,7 +6274,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -6287,17 +6289,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>M15_GYM_BASE_COAT_SATIN_STEEL_GRAYMET_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -6317,7 +6319,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -6332,22 +6334,22 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>M15_GYM_BASE_COAT_SATIN_STEEL_GRAYMET_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -6362,7 +6364,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6384,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -6407,7 +6409,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -6422,17 +6424,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -6452,7 +6454,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -6467,17 +6469,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -6497,7 +6499,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6519,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -6542,7 +6544,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -6557,17 +6559,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -6587,7 +6589,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -6602,17 +6604,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -6632,7 +6634,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -6647,17 +6649,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -6677,37 +6679,37 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>(GYM) BASE COAT SATIN STEEL GRAYMET</t>
+          <t>(GAN) BASE COAT SWITCHBLADE SILVER</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6722,7 +6724,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -6737,17 +6739,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>M16_GAN_BASE_COAT_SWITCHBLADE_SILVER_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -6767,7 +6769,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -6782,22 +6784,22 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>M16_GAN_BASE_COAT_SWITCHBLADE_SILVER_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -6812,7 +6814,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -6832,12 +6834,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -6857,7 +6859,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -6872,17 +6874,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -6902,7 +6904,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -6917,17 +6919,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -6947,7 +6949,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -6967,12 +6969,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6992,7 +6994,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -7007,17 +7009,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -7037,7 +7039,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -7052,17 +7054,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -7082,7 +7084,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -7097,17 +7099,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -7127,37 +7129,37 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>(GAN) BASE COAT SWITCHBLADE SILVER</t>
+          <t>(GL8) BASE COAT RED-E OR NOT RED MET-3</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -7172,7 +7174,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -7187,17 +7189,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>M17_GL8_BASE_COAT_RED_E_OR_NOT_RED_MET_3_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -7217,7 +7219,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -7232,22 +7234,22 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>M17_GL8_BASE_COAT_RED_E_OR_NOT_RED_MET_3_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -7262,7 +7264,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -7282,12 +7284,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -7307,7 +7309,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -7322,17 +7324,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -7352,7 +7354,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -7367,17 +7369,17 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -7397,7 +7399,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -7417,12 +7419,12 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -7442,7 +7444,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -7457,17 +7459,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -7487,7 +7489,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -7502,17 +7504,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -7532,7 +7534,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -7547,17 +7549,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -7577,37 +7579,37 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>(GL8) BASE COAT RED-E OR NOT RED MET-3</t>
+          <t>(GUM) BASE COAT SEEKER MET 3</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -7622,7 +7624,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -7637,17 +7639,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>M18_GUM_BASE_COAT_SEEKER_MET_3_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -7667,7 +7669,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -7682,22 +7684,22 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>M18_GUM_BASE_COAT_SEEKER_MET_3_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -7712,7 +7714,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -7732,12 +7734,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -7757,7 +7759,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7774,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -7802,7 +7804,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -7817,17 +7819,17 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -7847,7 +7849,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -7867,12 +7869,12 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -7892,7 +7894,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -7907,17 +7909,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -7937,7 +7939,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -7952,17 +7954,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7982,7 +7984,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -7997,17 +7999,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -8027,37 +8029,37 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>(GUM) BASE COAT SEEKER MET 3</t>
+          <t>(G7G) BASE COAT ZEUS</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -8072,7 +8074,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -8087,17 +8089,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>M19_G7G_BASE_COAT_ZEUS_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -8117,7 +8119,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -8132,22 +8134,22 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>M19_G7G_BASE_COAT_ZEUS_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -8162,7 +8164,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -8182,12 +8184,12 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -8207,7 +8209,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -8222,17 +8224,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -8252,7 +8254,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -8267,17 +8269,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -8297,7 +8299,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8319,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -8342,7 +8344,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -8357,17 +8359,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -8387,7 +8389,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -8402,17 +8404,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -8432,7 +8434,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -8447,17 +8449,17 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -8477,37 +8479,37 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>(G7G) BASE COAT ZEUS</t>
+          <t>(GZ8) BASE COAT SOME KINDA BLUE</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -8522,7 +8524,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -8537,17 +8539,17 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>M20_GZ8_BASE_COAT_SOME_KINDA_BLUE_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -8567,7 +8569,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -8582,22 +8584,22 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>M20_GZ8_BASE_COAT_SOME_KINDA_BLUE_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -8612,7 +8614,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8634,12 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -8657,7 +8659,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -8672,17 +8674,17 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -8702,7 +8704,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -8717,17 +8719,17 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -8747,7 +8749,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -8767,12 +8769,12 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -8792,7 +8794,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -8807,17 +8809,17 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -8837,7 +8839,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -8852,17 +8854,17 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -8882,7 +8884,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -8897,17 +8899,17 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8927,37 +8929,37 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>(GZ8) BASE COAT SOME KINDA BLUE</t>
+          <t>(G5J) BASE COAT DARKMOON BLUE</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -8972,7 +8974,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -8987,17 +8989,17 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>M21_G5J_BASE_COAT_DARKMOON_BLUE_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -9017,7 +9019,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -9032,22 +9034,22 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>M21_G5J_BASE_COAT_DARKMOON_BLUE_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -9062,7 +9064,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9084,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -9107,7 +9109,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -9122,17 +9124,17 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -9152,7 +9154,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -9167,17 +9169,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -9197,7 +9199,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -9217,12 +9219,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -9242,7 +9244,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -9257,17 +9259,17 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -9287,7 +9289,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -9302,17 +9304,17 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -9332,7 +9334,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -9347,17 +9349,17 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -9377,37 +9379,37 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>(G5J) BASE COAT DARKMOON BLUE</t>
+          <t>(G4V) BASE COAT POW ZINGA MET-3</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -9422,7 +9424,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items. Reviewer: silver-metallic refinish basecoat SDS used as generic proxy for all colours.</t>
         </is>
       </c>
     </row>
@@ -9437,17 +9439,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>M22_G4V_BASE_COAT_POW_ZINGA_MET_3_SDS_EQUIV.pdf</t>
+          <t>M11_GAZ_BASE_COAT_SUMMIT_WHITE_2C1B_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://msds.glasurit.com/files/53157504_MSDS_UN_EN.PDF</t>
+          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -9467,7 +9469,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; WebFetch blocked (host not in allowed network). Refinish, not OEM-line; generic solvent-borne metallic basecoat hazard profile proxy. Shared by all group C items.</t>
+          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
         </is>
       </c>
     </row>
@@ -9482,22 +9484,22 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>M22_G4V_BASE_COAT_POW_ZINGA_MET_3_TDS_EQUIV.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://msp.images.akzonobel.com/prd/dh/emebam/documents/b2/67/6f/d7/tds_s10403_5265_autobase_plus_ce.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -9512,7 +9514,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Seen in search results; not fetched (WebFetch network-blocked). Refinish basecoat duplicating OEM solid/metallic/pearl finishes; NOT the plant's OEM line product. Shared by all group C items.</t>
+          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
         </is>
       </c>
     </row>
@@ -9532,12 +9534,12 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_23_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -9557,7 +9559,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (library.e.abb.com not in allowed network).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -9572,17 +9574,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -9602,7 +9604,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
         </is>
       </c>
     </row>
@@ -9617,17 +9619,17 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_series_brochure.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -9647,7 +9649,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked. No dedicated RB1000-SSA datasheet found.</t>
+          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9669,12 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoMCC3_20_datasheet.pdf</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -9692,7 +9694,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>From search results; fetch blocked (www.durr.com). German version: duerr-datenblatt-ecobell3-de.pdf in same folder.</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
@@ -9707,17 +9709,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoMCC3_20_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply_P_brochure.pdf</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-mcc-3-20.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -9737,7 +9739,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
         </is>
       </c>
     </row>
@@ -9752,17 +9754,17 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply_P_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/08_Special_Events/03_ready2integrate_2019/duerr-Station-EcoSupplyP-BasicSinglePass.pdf</t>
+          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -9782,7 +9784,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>From search results; slide deck, not formal datasheet. No EcoRP E043i datasheet found.</t>
+          <t>From search results; URL contains a space (encode as %20).</t>
         </is>
       </c>
     </row>
@@ -9797,17 +9799,17 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_15_datasheet.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanucamerica.com/cmsmedia/datasheets/P-250iB_Product Information_330.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -9827,32 +9829,32 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>From search results; URL contains a space (encode as %20).</t>
+          <t>From search results; not fetched.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>(G4V) BASE COAT POW ZINGA MET-3</t>
+          <t>BASE TYPE THINNER</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_brochure.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -9872,7 +9874,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>From search results; not fetched.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9894,12 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -9923,31 +9925,31 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>BASE TYPE THINNER</t>
+          <t>TOP CLEAR HITEC 2000</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Material: brochure</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://www.ppg.com/en-US/autocoatings/products/clearcoats</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -9957,12 +9959,12 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. HTML page, not PDF. Name similarity only; no evidence PPG supplies Asaka.</t>
         </is>
       </c>
     </row>
@@ -9977,17 +9979,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Material: brochure</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>M24_TOP_CLEAR_HITEC_2000_brochure_EQUIV.pdf</t>
+          <t>M24_TOP_CLEAR_HITEC_2000_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.ppg.com/en-US/autocoatings/products/clearcoats</t>
+          <t>https://www.kccworld.co.kr/techdoc/c01/cvt/C01F202301250054173eng.pdf</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -10007,7 +10009,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. HTML page, not PDF. Name similarity only; no evidence PPG supplies Asaka.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. KCC 2K refinish clear on manufacturer site; loose family equivalent, not OEM 1K.</t>
         </is>
       </c>
     </row>
@@ -10022,22 +10024,22 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>M24_TOP_CLEAR_HITEC_2000_TDS_EQUIV.pdf</t>
+          <t>EQ_Durr_EcoRP_E043i_datasheet.pdf</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.kccworld.co.kr/techdoc/c01/cvt/C01F202301250054173eng.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/07_Paint_robots/01_Paint_Robots_Automotive/duerr-datasheet-ecorp-e043i-en.pdf</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -10052,7 +10054,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. KCC 2K refinish clear on manufacturer site; loose family equivalent, not OEM 1K.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10074,12 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoRP_E043i_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/07_Paint_robots/01_Paint_Robots_Automotive/duerr-datasheet-ecorp-e043i-en.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -10112,17 +10114,17 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -10157,17 +10159,17 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_FlexPainter_brochure.pdf</t>
+          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/396b885928754b56867a589c03bd43ab/IRB5500-Flex-RP50010EN-Rev.G.pdf</t>
+          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -10202,17 +10204,17 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_IRB_5500_22_datasheet.pdf</t>
+          <t>EQ_ABB_RB1000i_brochure.pdf</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/439e4e0991f741c48d0189710ac6edd4/IRB%205500-22_Datasheet_US%20Letter.pdf</t>
+          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -10232,7 +10234,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Presentation incl. data sheet section; no standalone RB1000 datasheet PDF found.</t>
         </is>
       </c>
     </row>
@@ -10247,17 +10249,17 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Jihoz: datasheet</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>EQ_ABB_RB1000i_brochure.pdf</t>
+          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://library.e.abb.com/public/b2995ed8b28a48ecb03c0267deaccb5d/RB1000i-Series-Presentation.pdf</t>
+          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -10277,7 +10279,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. Presentation incl. data sheet section; no standalone RB1000 datasheet PDF found.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10299,12 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>EQ_FANUC_P_250iB_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.fanuc.co.jp/en/product/catalog/pdf/robot/RP-250iB(E)-02a.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -10328,11 +10330,11 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>TOP CLEAR HITEC 2000</t>
+          <t>CLEAR THINNER</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -10342,7 +10344,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10373,11 +10375,11 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>CLEAR THINNER</t>
+          <t>CLEANING THINNER</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -10387,12 +10389,12 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell_Cleaner_D2_EcoBell_PurgeBox_datasheet.pdf</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/03_Atomizer_Cleaning/duerr-datasheet-ecobell-cleander-d2-ecobell-purgebox-en.pdf</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -10412,7 +10414,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. (sic 'cleander' in Dürr filename)</t>
         </is>
       </c>
     </row>
@@ -10432,12 +10434,12 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell_Cleaner_D2_EcoBell_PurgeBox_datasheet.pdf</t>
+          <t>EQ_Durr_EcoBell3_datasheet.pdf</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/03_Atomizer_Cleaning/duerr-datasheet-ecobell-cleander-d2-ecobell-purgebox-en.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -10457,7 +10459,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only. (sic 'cleander' in Dürr filename)</t>
+          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
         </is>
       </c>
     </row>
@@ -10477,12 +10479,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoBell3_datasheet.pdf</t>
+          <t>EQ_Durr_EcoSupply2_Core_datasheet.pdf</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/02_Paint_Shop_Application_Technology/06_Paint_Application/01_EcoBell_Rotary_Atomizer/duerr-datasheet-ecobell3-en.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -10508,31 +10510,31 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>CLEANING THINNER</t>
+          <t>DISK BRAKE FLUID DOT-4 PLUS (A/T and M/T)</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: datasheet</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_EcoSupply2_Core_datasheet.pdf</t>
+          <t>M27_DISK_BRAKE_FLUID_DOT_4_PLUS_A_T_and_M_T_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/09_MISC/19_Digital_Press_Kit/duerr-eco-supply-2-core.pdf</t>
+          <t>https://www.q8oils.com/wp-content/uploads/2025/11/Q8-Brake-Fluid-DOT-4plus_en.pdf</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -10547,7 +10549,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>WebFetch blocked in this session (host not in allowed network domains); URL seen in WebSearch results only.</t>
+          <t>Equivalent DOT 4+ PDS (dry boiling point min 260 C) for property reference; not the CROWN product. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10562,17 +10564,17 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>M27_DISK_BRAKE_FLUID_DOT_4_PLUS_A_T_and_M_T_TDS_EQUIV.pdf</t>
+          <t>M27_DISK_BRAKE_FLUID_DOT_4_PLUS_A_T_and_M_T_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.q8oils.com/wp-content/uploads/2025/11/Q8-Brake-Fluid-DOT-4plus_en.pdf</t>
+          <t>https://www.biketeile-service.de/media/attachment/pdf/sida_en_5585513.pdf</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -10592,7 +10594,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Equivalent DOT 4+ PDS (dry boiling point min 260 C) for property reference; not the CROWN product. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Equivalent DOT 4 Plus SDS (UK REACH format); generic glycol-ether hazard data. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10607,22 +10609,22 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>M27_DISK_BRAKE_FLUID_DOT_4_PLUS_A_T_and_M_T_SDS_EQUIV.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.biketeile-service.de/media/attachment/pdf/sida_en_5585513.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -10637,7 +10639,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Equivalent DOT 4 Plus SDS (UK REACH format); generic glycol-ether hazard data. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10657,12 +10659,12 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -10682,7 +10684,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10704,12 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -10727,37 +10729,37 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>DISK BRAKE FLUID DOT-4 PLUS (A/T and M/T)</t>
+          <t>POWER STRG OIL DEXRON-VI GM N10060</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
+          <t>https://shop.sclubricants.com/pub/media/pds/pennzoil/Pennzoil-ATF-Dexron-VI-Technical-Datasheet.pdf</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -10772,7 +10774,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>States 'Meets GM specification GMN10060' (per search snippet). URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10792,12 +10794,12 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://shop.sclubricants.com/pub/media/pds/pennzoil/Pennzoil-ATF-Dexron-VI-Technical-Datasheet.pdf</t>
+          <t>https://partner.ravenol.de/storage/app/media/product-pdf/Tds_1211105_en.pdf</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -10817,7 +10819,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>States 'Meets GM specification GMN10060' (per search snippet). URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Lists GMN 10060, GM licence J-60331 (per search snippet). URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10832,17 +10834,17 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV_2.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://partner.ravenol.de/storage/app/media/product-pdf/Tds_1211105_en.pdf</t>
+          <t>https://www.ravenol.de/storage/app/uploads/share/SDB/Sdb_RAVENOL%20ATF%20DEXRON%20VI_1211105_en_ALL.pdf</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -10862,7 +10864,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Lists GMN 10060, GM licence J-60331 (per search snippet). URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>SDS matching the Ravenol TDS above. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10882,12 +10884,12 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.ravenol.de/storage/app/uploads/share/SDB/Sdb_RAVENOL%20ATF%20DEXRON%20VI_1211105_en_ALL.pdf</t>
+          <t>https://msds.fmpco.com/images/fmp_msds/19287624_DexronVI_2014.pdf</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -10907,7 +10909,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>SDS matching the Ravenol TDS above. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>GM-branded genuine Dexron-VI SDS; closest to GM factory fluid. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10922,22 +10924,22 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV_2.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://msds.fmpco.com/images/fmp_msds/19287624_DexronVI_2014.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -10952,7 +10954,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>GM-branded genuine Dexron-VI SDS; closest to GM factory fluid. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -10972,12 +10974,12 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -10997,7 +10999,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11019,12 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -11042,37 +11044,37 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>POWER STRG OIL DEXRON-VI GM N10060</t>
+          <t>ANTIFREEZE DX-COOL CONCENTRATE RED</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: brochure</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>M29_ANTIFREEZE_DX_COOL_CONCENTRATE_RED_brochure_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
+          <t>https://pwr.com.au/app/uploads/2022/08/ACDelco-Coolant-FAQ.pdf</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -11087,7 +11089,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>GM DEX-COOL red concentrate reference (SG 1.130); not Felix. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11102,17 +11104,17 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Material: brochure</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>M29_ANTIFREEZE_DX_COOL_CONCENTRATE_RED_brochure_EQUIV.pdf</t>
+          <t>M29_ANTIFREEZE_DX_COOL_CONCENTRATE_RED_PDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://pwr.com.au/app/uploads/2022/08/ACDelco-Coolant-FAQ.pdf</t>
+          <t>https://shop.sclubricants.com/pub/media/pds/shell/Shell-Dexcool-Antifreeze-Coolant-50_50-datasheet.pdf</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
@@ -11132,7 +11134,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>GM DEX-COOL red concentrate reference (SG 1.130); not Felix. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>DEX-COOL type ethylene glycol OAT coolant PDS. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11152,12 +11154,12 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>M29_ANTIFREEZE_DX_COOL_CONCENTRATE_RED_PDS_EQUIV.pdf</t>
+          <t>M29_ANTIFREEZE_DX_COOL_CONCENTRATE_RED_PDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://shop.sclubricants.com/pub/media/pds/shell/Shell-Dexcool-Antifreeze-Coolant-50_50-datasheet.pdf</t>
+          <t>https://kostusa.com/wp-content/uploads/2022/09/NEW-PDS-DefendAL-DexCoolAutomotive.pdf</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -11177,7 +11179,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>DEX-COOL type ethylene glycol OAT coolant PDS. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>DEX-COOL type coolant PDS. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11192,22 +11194,22 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>M29_ANTIFREEZE_DX_COOL_CONCENTRATE_RED_PDS_EQUIV_2.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://kostusa.com/wp-content/uploads/2022/09/NEW-PDS-DefendAL-DexCoolAutomotive.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -11222,7 +11224,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>DEX-COOL type coolant PDS. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11242,12 +11244,12 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -11267,7 +11269,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11287,12 +11289,12 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -11312,17 +11314,17 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>ANTIFREEZE DX-COOL CONCENTRATE RED</t>
+          <t>T/M OIL</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -11332,12 +11334,12 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -11357,7 +11359,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11377,12 +11379,12 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -11402,7 +11404,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11424,12 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -11447,37 +11449,37 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>T/M OIL</t>
+          <t>T/M OIL MANUAL SH XGP 75W85 GL-4</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>M31_T_M_OIL_MANUAL_SH_XGP_75W85_GL_4_PDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
+          <t>https://www.supercheapauto.co.nz/on/demandware.static/-/Library-Sites-supercheap-shared-library/default/dwe49223ef/productsheets/396350_342312.pdf</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -11492,7 +11494,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Equivalent full-synthetic 75W-85 GL-4 data sheet for property reference only. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -11507,22 +11509,22 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Material: brochure</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>M31_T_M_OIL_MANUAL_SH_XGP_75W85_GL_4_PDS_EQUIV.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.supercheapauto.co.nz/on/demandware.static/-/Library-Sites-supercheap-shared-library/default/dwe49223ef/productsheets/396350_342312.pdf</t>
+          <t>https://parts.gmparts.com/product/acdelco-gm-original-equipment-xgp-sae-75w-85-manual-transmission-fluid-1-qt-19351859</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -11532,12 +11534,12 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Equivalent full-synthetic 75W-85 GL-4 data sheet for property reference only. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>HTML product page (official GM listing)</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11559,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11602,7 +11604,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11647,7 +11649,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11692,7 +11694,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>M32_A_T_OIL_DEXRON_VI_TDS_EQUIV.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11737,7 +11739,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>M32_A_T_OIL_DEXRON_VI_TDS_EQUIV_2.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_TDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11782,7 +11784,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>M32_A_T_OIL_DEXRON_VI_SDS_EQUIV.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11827,7 +11829,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>M32_A_T_OIL_DEXRON_VI_SDS_EQUIV_2.pdf</t>
+          <t>M28_POWER_STRG_OIL_DEXRON_VI_GM_N10060_SDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11872,7 +11874,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11917,7 +11919,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -11962,7 +11964,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12142,7 +12144,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12187,7 +12189,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12232,7 +12234,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12263,31 +12265,31 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>TETRAFLUOROETHANE HFC-134a</t>
+          <t>FUEL</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: manual</t>
+          <t>Material: standard</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_Somac_filling_stations_refrigerant_proce_manual.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/somac-filling.de/Company/KA014_QW_V1.0_Instructions_for_the_Calibration_of_Process_Measurement_Equipment.pdf</t>
+          <t>https://meganorm.ru/mega_doc/norm/gost_gosudarstvennyj-standart/20/gost_32513-2013_mezhgosudarstvennyy_standart_topliva.html</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -12297,12 +12299,12 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Dürr Somac calibration instruction for process measurement equipment (refrigerant measurement); service document, not a brochure. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>HTML full text, not PDF. Superseded in Russia by GOST 32513-2023 from 03.02.2025. Uzbek O'zDSt equivalent text not found online. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12317,17 +12319,17 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Material: standard</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>M34_FUEL_standard_EQUIV.pdf</t>
+          <t>M34_FUEL_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://meganorm.ru/mega_doc/norm/gost_gosudarstvennyj-standart/20/gost_32513-2013_mezhgosudarstvennyy_standart_topliva.html</t>
+          <t>https://ina.hr/app/uploads/2024/06/Unleaded-Petrol_v22_EN.pdf</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -12347,7 +12349,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>HTML full text, not PDF. Superseded in Russia by GOST 32513-2023 from 03.02.2025. Uzbek O'zDSt equivalent text not found online. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Reputable REACH-format unleaded gasoline SDS. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12367,12 +12369,12 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>M34_FUEL_SDS_EQUIV.pdf</t>
+          <t>M34_FUEL_SDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://ina.hr/app/uploads/2024/06/Unleaded-Petrol_v22_EN.pdf</t>
+          <t>https://www.nis.rs/wp-content/uploads/2025/09/EN_SDS_UNLEADED-GASOLINE_GHS-ANNEXII-CLP_20250725_NIS-a.d.-Novi-Sad.pdf</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -12392,7 +12394,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Reputable REACH-format unleaded gasoline SDS. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Gazprom Neft-group refinery (NIS) gasoline SDS; generic. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12407,22 +12409,22 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>M34_FUEL_SDS_EQUIV_2.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.nis.rs/wp-content/uploads/2025/09/EN_SDS_UNLEADED-GASOLINE_GHS-ANNEXII-CLP_20250725_NIS-a.d.-Novi-Sad.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -12437,7 +12439,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Gazprom Neft-group refinery (NIS) gasoline SDS; generic. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12457,12 +12459,12 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -12482,7 +12484,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12502,12 +12504,12 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -12527,37 +12529,37 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>FUEL</t>
+          <t>WINDSHIELD WASHER (ETHANOL - 80%)</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>M35_WINDSHIELD_WASHER_ETHANOL_80_PDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
+          <t>https://sirv.eurol.com/eurol/PI/EN/EN_E502260_PI.pdf</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -12572,7 +12574,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Stated ethanol-based; flash point 23 C, density 0.91. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12587,17 +12589,17 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>M35_WINDSHIELD_WASHER_ETHANOL_80_PDS_EQUIV.pdf</t>
+          <t>M35_WINDSHIELD_WASHER_ETHANOL_80_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://sirv.eurol.com/eurol/PI/EN/EN_E502260_PI.pdf</t>
+          <t>https://www.msds.ford.com/documents/198426 G_GBEN.pdf</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -12617,7 +12619,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Stated ethanol-based; flash point 23 C, density 0.91. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>OEM screen wash SDS listing ethanol (CAS 64-17-5). URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12632,22 +12634,22 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>M35_WINDSHIELD_WASHER_ETHANOL_80_SDS_EQUIV.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.msds.ford.com/documents/198426 G_GBEN.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -12662,7 +12664,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>OEM screen wash SDS listing ethanol (CAS 64-17-5). URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12682,12 +12684,12 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_incl_Somac_filli_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/duerr-brochure-NEXT.assembly-english-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -12707,7 +12709,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Dürr final-assembly brochure covering conveyor, gluing, marriage, filling and testing modules; general, not a model datasheet. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
@@ -12727,12 +12729,12 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_NEXT_assembly_portfolio_newer_edition_brochure.pdf</t>
+          <t>EQ_Durr_Durr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/06_Final_Assembly_Systems/durr-NEXT.assembly-brochure-en-digital-low.pdf</t>
+          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -12752,37 +12754,37 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Newer edition of the final-assembly brochure; general. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>WINDSHIELD WASHER (ETHANOL - 80%)</t>
+          <t>BETASEAL / SikaFlex-250 UZ-1</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>EQ_D_rr_D_rr_Somac_GmbH_DXQ_filling_fill_stations_brochure.pdf</t>
+          <t>M36_BETASEAL_SikaFlex_250_UZ_1_PDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.durr.com/fileadmin/durr.com/01_Products/12_Software_Controls/DXQ/05_DXQfinalassembly/Filling/duerr-filling-case-study-en.pdf</t>
+          <t>https://deu.sika.com/dms/getdocument.get/7d702bec-814c-4eb8-805d-1ad0cb019466/sikaflex-250-dm-5.pdf</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -12797,7 +12799,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Case study (VW Dresden) on brake, radiator/coolant, battery thermal and A/C fill stations with DXQ software. URL taken from search results; WebFetch blocked by sandbox network policy (host not allowed), so content not opened.</t>
+          <t>From search results; WebFetch blocked (host not in allowed network). Search snippet: developed for direct glazing in automotive industry.</t>
         </is>
       </c>
     </row>
@@ -12817,12 +12819,12 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>M36_BETASEAL_SikaFlex_250_UZ_1_PDS_EQUIV.pdf</t>
+          <t>M36_BETASEAL_SikaFlex_250_UZ_1_PDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://deu.sika.com/dms/getdocument.get/7d702bec-814c-4eb8-805d-1ad0cb019466/sikaflex-250-dm-5.pdf</t>
+          <t>https://deu.sika.com/dms/getdocument.get/48aee572-deb8-4a11-85c7-8682134452bd/sikaflex-250-dp-2-plus-sikaboosterp-50.pdf</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -12842,7 +12844,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>From search results; WebFetch blocked (host not in allowed network). Search snippet: developed for direct glazing in automotive industry.</t>
+          <t>Accelerated variant for automated direct glazing; not fetched (network).</t>
         </is>
       </c>
     </row>
@@ -12862,12 +12864,12 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>M36_BETASEAL_SikaFlex_250_UZ_1_PDS_EQUIV_2.pdf</t>
+          <t>M36_BETASEAL_SikaFlex_250_UZ_1_PDS_EQUIV_3.pdf</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://deu.sika.com/dms/getdocument.get/48aee572-deb8-4a11-85c7-8682134452bd/sikaflex-250-dp-2-plus-sikaboosterp-50.pdf</t>
+          <t>https://egy.sika.com/dms/getdocument.get/ecf85750-dd7d-3490-9be2-3e36a8285895/Sikaflex</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -12887,7 +12889,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Accelerated variant for automated direct glazing; not fetched (network).</t>
+          <t>Old 2006 sheet per search snippet; not fetched.</t>
         </is>
       </c>
     </row>
@@ -12902,17 +12904,17 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>M36_BETASEAL_SikaFlex_250_UZ_1_PDS_EQUIV_3.pdf</t>
+          <t>M36_BETASEAL_SikaFlex_250_UZ_1_SDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://egy.sika.com/dms/getdocument.get/ecf85750-dd7d-3490-9be2-3e36a8285895/Sikaflex</t>
+          <t>https://kor.sika.com/dms/getdocument.get/5577a611-f6de-438f-ab00-dbfea96a137d/MSDS_Sikaflex%C2%AE-250PC(SSC)_EN_251226_AA00068-0000000296.pdf</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -12932,7 +12934,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Old 2006 sheet per search snippet; not fetched.</t>
+          <t>Different 250 variant; only SDS of 250 family found. Request UZ-1 SDS from Sika.</t>
         </is>
       </c>
     </row>
@@ -12947,17 +12949,17 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>M36_BETASEAL_SikaFlex_250_UZ_1_SDS_EQUIV.pdf</t>
+          <t>M36_BETASEAL_SikaFlex_250_UZ_1_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://kor.sika.com/dms/getdocument.get/5577a611-f6de-438f-ab00-dbfea96a137d/MSDS_Sikaflex%C2%AE-250PC(SSC)_EN_251226_AA00068-0000000296.pdf</t>
+          <t>https://dupont.materialdatacenter.com/gb/products/pdf/SI/BETASEAL%E2%84%A2%20U-838HV-gb.pdf</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -12977,7 +12979,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Different 250 variant; only SDS of 250 family found. Request UZ-1 SDS from Sika.</t>
+          <t>Representative BETASEAL OEM glazing urethane; not fetched.</t>
         </is>
       </c>
     </row>
@@ -12997,12 +12999,12 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>M36_BETASEAL_SikaFlex_250_UZ_1_TDS_EQUIV.pdf</t>
+          <t>M36_BETASEAL_SikaFlex_250_UZ_1_TDS_EQUIV_2.pdf</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://dupont.materialdatacenter.com/gb/products/pdf/SI/BETASEAL%E2%84%A2%20U-838HV-gb.pdf</t>
+          <t>https://www.pksupplies.com/sites/default/files/datasheets/dupont-betaseal-primerless-to-glass-adhesive-data-sheet.pdf</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -13022,7 +13024,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Representative BETASEAL OEM glazing urethane; not fetched.</t>
+          <t>Distributor-hosted copy.</t>
         </is>
       </c>
     </row>
@@ -13037,22 +13039,22 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Jihoz: manual</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>M36_BETASEAL_SikaFlex_250_UZ_1_TDS_EQUIV_2.pdf</t>
+          <t>EQ_Graco_Therm_O_Flow_200_manual.pdf</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.pksupplies.com/sites/default/files/datasheets/dupont-betaseal-primerless-to-glass-adhesive-data-sheet.pdf</t>
+          <t>https://graco.com/content/dam/graco/tech_documents/manuals/334/334130/334130EN.pdf</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -13067,7 +13069,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Distributor-hosted copy.</t>
+          <t>From search; WebFetch blocked.</t>
         </is>
       </c>
     </row>
@@ -13087,12 +13089,12 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_Therm_O_Flow_200_manual.pdf</t>
+          <t>EQ_Graco_Therm_O_Flow_EasyKey_200_L_manual.pdf</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://graco.com/content/dam/graco/tech_documents/manuals/334/334130/334130EN.pdf</t>
+          <t>https://www.graco.com/content/dam/graco/tech_documents/manuals/311/311208/311208EN-S.pdf</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -13112,7 +13114,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>From search; WebFetch blocked.</t>
+          <t>Search snippet: covers 200 L drum size.</t>
         </is>
       </c>
     </row>
@@ -13127,17 +13129,17 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: manual</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_Therm_O_Flow_EasyKey_200_L_manual.pdf</t>
+          <t>EQ_Graco_PCF_brochure.pdf</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.graco.com/content/dam/graco/tech_documents/manuals/311/311208/311208EN-S.pdf</t>
+          <t>https://www.graco.com/content/dam/graco/aftd/literature/brochures/340305/340305EN-D.pdf</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -13157,7 +13159,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Search snippet: covers 200 L drum size.</t>
+          <t>Handles ambient/warm/hot melt up to 204 C per snippet.</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13179,12 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_PCF_brochure.pdf</t>
+          <t>EQ_Graco_Therm_O_Flow_Warm_Melt_20_brochure.pdf</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.graco.com/content/dam/graco/aftd/literature/brochures/340305/340305EN-D.pdf</t>
+          <t>https://gww.graco.com/content/dam/graco/aftd/literature/brochures/350422/350422ENEU-A.pdf</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -13202,17 +13204,17 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Handles ambient/warm/hot melt up to 204 C per snippet.</t>
+          <t>Lists window glazing / urethanes; 20 L (pail) version.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>BETASEAL / SikaFlex-250 UZ-1</t>
+          <t>ADHESIVE-HDLNG T/PNL</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -13222,12 +13224,12 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_Therm_O_Flow_Warm_Melt_20_brochure.pdf</t>
+          <t>EQ_Graco_PCF_brochure.pdf</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://gww.graco.com/content/dam/graco/aftd/literature/brochures/350422/350422ENEU-A.pdf</t>
+          <t>https://www.graco.com/content/dam/graco/aftd/literature/brochures/340305/340305EN-D.pdf</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -13247,37 +13249,37 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>Lists window glazing / urethanes; 20 L (pail) version.</t>
+          <t>Not fetched.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>ADHESIVE-HDLNG T/PNL</t>
+          <t>RKB 0101S</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_PCF_brochure.pdf</t>
+          <t>M38_RKB_0101S_PDS.pdf</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.graco.com/content/dam/graco/aftd/literature/brochures/340305/340305EN-D.pdf</t>
+          <t>https://gbr.sika.com/dam/dms/gb01/f/sika-primer-209-d.pdf</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -13292,7 +13294,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>Not fetched.</t>
+          <t>Per snippet; brush/felt/foam applicator, ~50 ml/m2. Not fetched (DNS blocked).</t>
         </is>
       </c>
     </row>
@@ -13312,12 +13314,12 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>M38_RKB_0101S_PDS.pdf</t>
+          <t>M38_RKB_0101S_PDS_2.pdf</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://gbr.sika.com/dam/dms/gb01/f/sika-primer-209-d.pdf</t>
+          <t>https://industry.sika.com/dam/dms/ca01/x/sika-primer-209-d.pdf</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -13337,7 +13339,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Per snippet; brush/felt/foam applicator, ~50 ml/m2. Not fetched (DNS blocked).</t>
+          <t>Alternate host.</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13354,17 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>M38_RKB_0101S_PDS_2.pdf</t>
+          <t>M38_RKB_0101S_SDS.pdf</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://industry.sika.com/dam/dms/ca01/x/sika-primer-209-d.pdf</t>
+          <t>https://gbr.sika.com/dms/getdocument.get/fc7c9a30-2929-424b-9f85-2cb6042f8040/Sika%C2%AE%20Primer-209%20D%20SDS.pdf</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -13382,7 +13384,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Alternate host.</t>
+          <t>Not fetched.</t>
         </is>
       </c>
     </row>
@@ -13402,12 +13404,12 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>M38_RKB_0101S_SDS.pdf</t>
+          <t>M38_RKB_0101S_SDS_2.pdf</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://gbr.sika.com/dms/getdocument.get/fc7c9a30-2929-424b-9f85-2cb6042f8040/Sika%C2%AE%20Primer-209%20D%20SDS.pdf</t>
+          <t>https://nzl.sika.com/dam/dms/nz01/3/Primer%20209D%20-%20MSDS.pdf</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -13427,7 +13429,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Not fetched.</t>
+          <t>Newer EN SDS.</t>
         </is>
       </c>
     </row>
@@ -13447,12 +13449,12 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>M38_RKB_0101S_SDS_2.pdf</t>
+          <t>M38_RKB_0101S_SDS_3.pdf</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://nzl.sika.com/dam/dms/nz01/3/Primer%20209D%20-%20MSDS.pdf</t>
+          <t>https://tur.sika.com/dms/getdocument.get/5aa00d1a-99ca-4747-888a-eda15c33f505/Sika%20Primer-209D%20MSDS%20EN.pdf</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -13472,32 +13474,32 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>Newer EN SDS.</t>
+          <t>Not fetched.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>RKB 0101S</t>
+          <t>RKB 0401S</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>M38_RKB_0101S_SDS_3.pdf</t>
+          <t>M39_RKB_0401S_PDS.pdf</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://tur.sika.com/dms/getdocument.get/5aa00d1a-99ca-4747-888a-eda15c33f505/Sika%20Primer-209D%20MSDS%20EN.pdf</t>
+          <t>https://industry.sika.com/dam/dms/us01/w/sika_primer-206_gp.pdf</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -13517,7 +13519,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Not fetched.</t>
+          <t>Snippet: 36% solids, brush/felt/foam, ~50 ml/m2. Not fetched.</t>
         </is>
       </c>
     </row>
@@ -13537,12 +13539,12 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>M39_RKB_0401S_PDS.pdf</t>
+          <t>M39_RKB_0401S_PDS_2.pdf</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://industry.sika.com/dam/dms/us01/w/sika_primer-206_gp.pdf</t>
+          <t>https://industry.sika.com/dam/dms/ch01/f/sika-primer-206-g-plus-p.pdf</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -13562,7 +13564,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Snippet: 36% solids, brush/felt/foam, ~50 ml/m2. Not fetched.</t>
+          <t>Alternate.</t>
         </is>
       </c>
     </row>
@@ -13577,17 +13579,17 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>M39_RKB_0401S_PDS_2.pdf</t>
+          <t>M39_RKB_0401S_SDS.pdf</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://industry.sika.com/dam/dms/ch01/f/sika-primer-206-g-plus-p.pdf</t>
+          <t>https://usa.sika.com/dam/dms/us01/s/Sika-Primer-206-G-P.pdf</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -13607,7 +13609,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>Alternate.</t>
+          <t>Not fetched.</t>
         </is>
       </c>
     </row>
@@ -13627,12 +13629,12 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>M39_RKB_0401S_SDS.pdf</t>
+          <t>M39_RKB_0401S_SDS_2.pdf</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://usa.sika.com/dam/dms/us01/s/Sika-Primer-206-G-P.pdf</t>
+          <t>https://nzl.sika.com/dam/dms/nz01/t/Sika%C2%AE%20Primer-206%20G%20plus%20P%20-%20SDS%20-%201122.pdf</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -13672,12 +13674,12 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>M39_RKB_0401S_SDS_2.pdf</t>
+          <t>M39_RKB_0401S_SDS_3.pdf</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://nzl.sika.com/dam/dms/nz01/t/Sika%C2%AE%20Primer-206%20G%20plus%20P%20-%20SDS%20-%201122.pdf</t>
+          <t>https://srb.sika.com/dms/getdocument.get/a237532a-c159-4c08-8f85-74a2b307eb7d_rs01/sds-sika-primer-206g-plus-p.pdf</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -13703,26 +13705,26 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>RKB 0401S</t>
+          <t>BETAPRIME</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>M39_RKB_0401S_SDS_3.pdf</t>
+          <t>M40_BETAPRIME_PDS.pdf</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://srb.sika.com/dms/getdocument.get/a237532a-c159-4c08-8f85-74a2b307eb7d_rs01/sds-sika-primer-206g-plus-p.pdf</t>
+          <t>https://industry.sika.com/dam/dms/us01/l/sika_aktivator-100.pdf</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -13742,7 +13744,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Not fetched.</t>
+          <t>Snippet: wipe-on/wipe-off with lint-free tissue, ~20 ml/m2. Not fetched.</t>
         </is>
       </c>
     </row>
@@ -13757,17 +13759,17 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Material: SDS</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>M40_BETAPRIME_PDS.pdf</t>
+          <t>M40_BETAPRIME_SDS.pdf</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://industry.sika.com/dam/dms/us01/l/sika_aktivator-100.pdf</t>
+          <t>https://gbr.sika.com/dam/dms/gb01/v/sds-sika-aktivator-100.pdf</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -13787,7 +13789,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>Snippet: wipe-on/wipe-off with lint-free tissue, ~20 ml/m2. Not fetched.</t>
+          <t>Not fetched.</t>
         </is>
       </c>
     </row>
@@ -13807,12 +13809,12 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>M40_BETAPRIME_SDS.pdf</t>
+          <t>M40_BETAPRIME_SDS_2.pdf</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://gbr.sika.com/dam/dms/gb01/v/sds-sika-aktivator-100.pdf</t>
+          <t>https://aus.sika.com/dam/dms/au01/f/sds-sika-aktivator-100.pdf</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -13847,22 +13849,22 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Material: SDS</t>
+          <t>Material: TDS</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>M40_BETAPRIME_SDS_2.pdf</t>
+          <t>M40_BETAPRIME_TDS_EQUIV.pdf</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://aus.sika.com/dam/dms/au01/f/sds-sika-aktivator-100.pdf</t>
+          <t>https://dupont.materialdatacenter.com/gb/products/pdf/US/BETAPRIME%E2%84%A2%205504G%20NO%20SHAKE-gb-US.pdf</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -13877,32 +13879,32 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>Not fetched.</t>
+          <t>DuPont alternate if BETASEAL system used; is a black primer, not a cleaner.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>BETAPRIME</t>
+          <t>RAD 11724</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Material: TDS</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>M40_BETAPRIME_TDS_EQUIV.pdf</t>
+          <t>M40_BETAPRIME_PDS.pdf</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://dupont.materialdatacenter.com/gb/products/pdf/US/BETAPRIME%E2%84%A2%205504G%20NO%20SHAKE-gb-US.pdf</t>
+          <t>https://industry.sika.com/dam/dms/us01/l/sika_aktivator-100.pdf</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
@@ -13922,37 +13924,37 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>DuPont alternate if BETASEAL system used; is a black primer, not a cleaner.</t>
+          <t>Only if spec SIKA-100-UZ really means Aktivator-100; unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>RAD 11724</t>
+          <t>LUBRICANT-WHL PILOT HOLE</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Jihoz: manual</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>M41_RAD_11724_PDS_EQUIV.pdf</t>
+          <t>EQ_Graco_Fire_Ball_pumps_manual.pdf</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://industry.sika.com/dam/dms/us01/l/sika_aktivator-100.pdf</t>
+          <t>https://graco.com/content/dam/graco/tech_documents/manuals/309/309868/historic/309868EN-B.pdf</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -13967,7 +13969,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Only if spec SIKA-100-UZ really means Aktivator-100; unconfirmed.</t>
+          <t>From search; not fetched.</t>
         </is>
       </c>
     </row>
@@ -13982,17 +13984,17 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: manual</t>
+          <t>Jihoz: brochure</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>EQ_Graco_Fire_Ball_pumps_manual.pdf</t>
+          <t>EQ_Lincoln_Equipment_range_brochure.pdf</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://graco.com/content/dam/graco/tech_documents/manuals/309/309868/historic/309868EN-B.pdf</t>
+          <t>https://petroleumservicecompany.com/content/pdfs/Lincoln_Equipment_Brochure.pdf</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -14012,37 +14014,37 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>From search; not fetched.</t>
+          <t>Distributor-hosted general brochure.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>LUBRICANT-WHL PILOT HOLE</t>
+          <t>LUBRICANT-CLU PLT HUB M/T</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Jihoz: brochure</t>
+          <t>Material: PDS</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>EQ_Lincoln_Equipment_range_brochure.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://petroleumservicecompany.com/content/pdfs/Lincoln_Equipment_Brochure.pdf</t>
+          <t>https://www.klueber.com/us/en/products-service/products/microlube-gny-202/9866/</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -14052,12 +14054,12 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>Distributor-hosted general brochure.</t>
+          <t>HTML page, not PDF; PDF download requires login per search snippet.</t>
         </is>
       </c>
     </row>
@@ -14077,12 +14079,12 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>M43_LUBRICANT_CLU_PLT_HUB_M_T_PDS.pdf</t>
+          <t>(veb-sahifa)</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.klueber.com/us/en/products-service/products/microlube-gny-202/9866/</t>
+          <t>https://klueber.com/uk/en/products-service/products/microlube-gny-202/9866</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -14097,12 +14099,12 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>yuklanmagan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>HTML page, not PDF; PDF download requires login per search snippet.</t>
+          <t>HTML product page; PI PDF requires Klüber login</t>
         </is>
       </c>
     </row>
@@ -14117,22 +14119,22 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Material: PDS</t>
+          <t>Jihoz: manual</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>M43_LUBRICANT_CLU_PLT_HUB_M_T_PDS_2.pdf</t>
+          <t>EQ_Graco_Fire_Ball_pumps_manual.pdf</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/862106522/MICROLUBE-GNY-202-017118-PI-EN-en</t>
+          <t>https://graco.com/content/dam/graco/tech_documents/manuals/309/309868/historic/309868EN-B.pdf</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -14147,57 +14149,12 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Third-party copy of product information.</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>LUBRICANT-CLU PLT HUB M/T</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>Jihoz: manual</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
-        <is>
-          <t>EQ_Graco_Fire_Ball_pumps_manual.pdf</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr">
-        <is>
-          <t>https://graco.com/content/dam/graco/tech_documents/manuals/309/309868/historic/309868EN-B.pdf</t>
-        </is>
-      </c>
-      <c r="F273" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G273" s="2" t="inlineStr">
-        <is>
-          <t>yo'q</t>
-        </is>
-      </c>
-      <c r="H273" s="2" t="inlineStr">
-        <is>
-          <t>yuklanmagan</t>
-        </is>
-      </c>
-      <c r="I273" s="2" t="inlineStr">
-        <is>
           <t>Not fetched.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I273"/>
+  <autoFilter ref="A1:I272"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14558,7 +14515,8 @@
           <t>Graco E-Flo SP electric supply system (D200/D200S 200 L drum ram) or Check-Mate/Dura-Flo ram: PVC plastisols are cold-pumped from drums with ram supply pumps; E-Flo SP is Graco's current electric sealant supply unit. (Therm-O-Flow is a HOT-melt unit and is less appropriate for PVC plastisol.) Representative.
 Dürr EcoShotMeter (piston dosing) + EcoGun2 3D applicator on sealing robot (EcoRP): Paint-shop sealing (PVC seam sealing, UBC, anti-chip) is typically robotic with shot-meter dosing; Dürr, Atlas Copco SCA and Graco PrecisionFlo are the main suppliers. Representative.
 Atlas Copco (SCA) SCA paint shop dispensing system (ASC 5000 controller, dosing units): SCA is widely used in GM/Korean paint shops for sealing; SYS 3000 not found, current paint-shop controller is ASC 5000. Representative.
-Graco PrecisionFlo XL: Legacy Graco sealer dosing common on older GM lines (UzAuto paint shop dates from 1996, modernised later).</t>
+Graco PrecisionFlo XL: Legacy Graco sealer dosing common on older GM lines (UzAuto paint shop dates from 1996, modernised later).
+Graco / Dürr Robotic airless / flat-stream spray package (e.g. Graco King airless pump + robot airless gun): Underbody coat and anti-chip PVC plastisol is normally sprayed airless or flat-stream by robots; added after independent review. No public datasheet confirmed.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -14616,7 +14574,8 @@
           <t>Graco E-Flo SP electric supply system (D200/D200S 200 L drum ram) or Check-Mate/Dura-Flo ram: PVC plastisols are cold-pumped from drums with ram supply pumps; E-Flo SP is Graco's current electric sealant supply unit. (Therm-O-Flow is a HOT-melt unit and is less appropriate for PVC plastisol.) Representative.
 Dürr EcoShotMeter (piston dosing) + EcoGun2 3D applicator on sealing robot (EcoRP): Paint-shop sealing (PVC seam sealing, UBC, anti-chip) is typically robotic with shot-meter dosing; Dürr, Atlas Copco SCA and Graco PrecisionFlo are the main suppliers. Representative.
 Atlas Copco (SCA) SCA paint shop dispensing system (ASC 5000 controller, dosing units): SCA is widely used in GM/Korean paint shops for sealing; SYS 3000 not found, current paint-shop controller is ASC 5000. Representative.
-Graco PrecisionFlo XL: Legacy Graco sealer dosing common on older GM lines (UzAuto paint shop dates from 1996, modernised later).</t>
+Graco PrecisionFlo XL: Legacy Graco sealer dosing common on older GM lines (UzAuto paint shop dates from 1996, modernised later).
+Graco / Dürr Robotic airless / flat-stream spray package (e.g. Graco King airless pump + robot airless gun): Underbody coat and anti-chip PVC plastisol is normally sprayed airless or flat-stream by robots; added after independent review. No public datasheet confirmed.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -14674,12 +14633,13 @@
           <t>Graco E-Flo SP electric supply system (D200/D200S 200 L drum ram) or Check-Mate/Dura-Flo ram: PVC plastisols are cold-pumped from drums with ram supply pumps; E-Flo SP is Graco's current electric sealant supply unit. (Therm-O-Flow is a HOT-melt unit and is less appropriate for PVC plastisol.) Representative.
 Dürr EcoShotMeter (piston dosing) + EcoGun2 3D applicator on sealing robot (EcoRP): Paint-shop sealing (PVC seam sealing, UBC, anti-chip) is typically robotic with shot-meter dosing; Dürr, Atlas Copco SCA and Graco PrecisionFlo are the main suppliers. Representative.
 Atlas Copco (SCA) SCA paint shop dispensing system (ASC 5000 controller, dosing units): SCA is widely used in GM/Korean paint shops for sealing; SYS 3000 not found, current paint-shop controller is ASC 5000. Representative.
-Graco PrecisionFlo XL: Legacy Graco sealer dosing common on older GM lines (UzAuto paint shop dates from 1996, modernised later).</t>
+Graco PrecisionFlo XL: Legacy Graco sealer dosing common on older GM lines (UzAuto paint shop dates from 1996, modernised later).
+Graco / Dürr Robotic airless / flat-stream spray package (e.g. Graco King airless pump + robot airless gun): Underbody coat and anti-chip PVC plastisol is normally sprayed airless or flat-stream by robots; added after independent review. No public datasheet confirmed.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Anti-chip PVC is robot/airless-sprayed on sills/wheel arches (wet-on-wet before primer). Spec 'P8201' not found publicly. Source row was duplicated. Local context: JV Uz-Dongju Paint Co (Asaka/Uzbekistan; UzAvtosanoat + Korean DongJu/KION) was set up to supply UzAuto with pretreatment chemicals (3750 t/yr), sealants (1250 t/yr) and automotive paints, and its 2024 privatisation required keeping GM-standard compliance. It is a plausible local maker/distributor of the RSB/RSU sealers and possibly pretreatment/ED materials (unconfirmed; uzdongju.uz not reachable from this session).</t>
+          <t>Anti-chip PVC is robot/airless-sprayed on sills/wheel arches (wet-on-wet before primer). Spec 'P8201' not found publicly. Source row was duplicated. Local context: JV Uz-Dongju Paint Co (Asaka/Uzbekistan; UzAvtosanoat + Korean DongJu/KION) was set up to supply UzAuto with pretreatment chemicals (3750 t/yr), sealants (1250 t/yr) and automotive paints, and its 2024 privatisation required keeping GM-standard compliance. It is a plausible local maker/distributor of the RSB/RSU sealers and possibly pretreatment/ED materials (unconfirmed; uzdongju.uz not reachable from this session). | REVIEW: Sikagard-6682 removed (water-based sound deadener, not PVC anti-chip).</t>
         </is>
       </c>
     </row>
@@ -15011,7 +14971,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>OEM solvent-borne basecoat, GM colour GD8 Burnt Coconut Metallic, GM Korea-style material spec KR-ADM-254 (180 L drum), 2-coat-1-bake (basecoat + clearcoat) system</t>
+          <t>GM colour 'Burnt Coconut Metallic' (GM Korea code 476A); source label GD8 (in GM global lists GD8 = Buick Coconut Pearl)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -15251,7 +15211,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>OEM solvent-borne basecoat, GM colour GL8 Red-E or Not Red Metallic, GM Korea-style material spec KR-ADM-122 (180 L drum), 2-coat-1-bake (basecoat + clearcoat) system</t>
+          <t>GM colour 'Red-E or Not Red Metallic' (GM codes GN6/WA454B; GX8 per PaintScratch); source label GL8 (GL8 in GM Spark list = Burning Hott Metallic 3)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15431,7 +15391,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>OEM solvent-borne basecoat, GM colour GZ8 Some Kinda Blue Metallic, GM Korea-style material spec KR-ADM-512U (180 L drum), 2-coat-1-bake (basecoat + clearcoat) system</t>
+          <t>GM colour 'Some Kinda Blue' (GM code GAO / WA619D); source label GZ8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -15851,7 +15811,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Korean shopping page (danawa plan 3938) lists '극동제연 크라운 브레이크액', linking CROWN brand to Kukdong Jeyon, a Korean OE fluid supplier; DOT4+ variant not seen directly. No Kukdong TDS/SDS PDF found publicly. No public evidence found of the actual filling equipment at UzAuto Motors Asaka; equipment is representative. Dürr Somac is the market leader in final-assembly fluid filling (approx. 2,900 stations in 44 countries) and is standard at GM plants; product pages (not PDFs) seen in search: durr.com/en/products/final-assembly/filling-technology/{line-filling-stations, compact-filling-stations, automated-filling-stations, filling-adapter} and .../nextassembly-of-the-future/proline-cube-filling-station. No 'EcoFill' product name was found on Dürr sources; current names are Somac ProLine Cube, ProLine, Compact X/CompStart, BlueStart, G4 Blue adapters.</t>
+          <t>Korean shopping page (danawa plan 3938) lists '극동제연 크라운 브레이크액', linking CROWN brand to Kukdong Jeyon, a Korean OE fluid supplier; DOT4+ variant not seen directly. No Kukdong TDS/SDS PDF found publicly. No public evidence found of the actual filling equipment at UzAuto Motors Asaka; equipment is representative. Dürr Somac is the market leader in final-assembly fluid filling (approx. 2,900 stations in 44 countries) and is standard at GM plants; product pages (not PDFs) seen in search: durr.com/en/products/final-assembly/filling-technology/{line-filling-stations, compact-filling-stations, automated-filling-stations, filling-adapter} and .../nextassembly-of-the-future/proline-cube-filling-station. No 'EcoFill' product name was found on Dürr sources; current names are Somac ProLine Cube, ProLine, Compact X/CompStart, BlueStart, G4 Blue adapters. | REVIEW: merged from 2 source rows (A/T and M/T), same SAP 200000259.</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15866,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Spec is generic GM Dexron-VI (GMN10060); actual supplier to UzAuto not identified. No public evidence found of the actual filling equipment at UzAuto Motors Asaka; equipment is representative. Dürr Somac is the market leader in final-assembly fluid filling (approx. 2,900 stations in 44 countries) and is standard at GM plants; product pages (not PDFs) seen in search: durr.com/en/products/final-assembly/filling-technology/{line-filling-stations, compact-filling-stations, automated-filling-stations, filling-adapter} and .../nextassembly-of-the-future/proline-cube-filling-station. No 'EcoFill' product name was found on Dürr sources; current names are Somac ProLine Cube, ProLine, Compact X/CompStart, BlueStart, G4 Blue adapters.</t>
+          <t>Spec is generic GM Dexron-VI (GMN10060); actual supplier to UzAuto not identified. No public evidence found of the actual filling equipment at UzAuto Motors Asaka; equipment is representative. Dürr Somac is the market leader in final-assembly fluid filling (approx. 2,900 stations in 44 countries) and is standard at GM plants; product pages (not PDFs) seen in search: durr.com/en/products/final-assembly/filling-technology/{line-filling-stations, compact-filling-stations, automated-filling-stations, filling-adapter} and .../nextassembly-of-the-future/proline-cube-filling-station. No 'EcoFill' product name was found on Dürr sources; current names are Somac ProLine Cube, ProLine, Compact X/CompStart, BlueStart, G4 Blue adapters. | REVIEW: GMN10060 (DEXRON-VI) superseded by GMW16444.</t>
         </is>
       </c>
     </row>
@@ -16126,7 +16086,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Same fluid family as id 28. Automatic transaxles (e.g. GM 6T40 built at GM Powertrain Uzbekistan) are typically filled at the powertrain plant. No public evidence found of the actual filling equipment at UzAuto Motors Asaka; equipment is representative. Dürr Somac is the market leader in final-assembly fluid filling (approx. 2,900 stations in 44 countries) and is standard at GM plants; product pages (not PDFs) seen in search: durr.com/en/products/final-assembly/filling-technology/{line-filling-stations, compact-filling-stations, automated-filling-stations, filling-adapter} and .../nextassembly-of-the-future/proline-cube-filling-station. No 'EcoFill' product name was found on Dürr sources; current names are Somac ProLine Cube, ProLine, Compact X/CompStart, BlueStart, G4 Blue adapters.</t>
+          <t>Same fluid family as id 28. Automatic transaxles (e.g. GM 6T40 built at GM Powertrain Uzbekistan) are typically filled at the powertrain plant. No public evidence found of the actual filling equipment at UzAuto Motors Asaka; equipment is representative. Dürr Somac is the market leader in final-assembly fluid filling (approx. 2,900 stations in 44 countries) and is standard at GM plants; product pages (not PDFs) seen in search: durr.com/en/products/final-assembly/filling-technology/{line-filling-stations, compact-filling-stations, automated-filling-stations, filling-adapter} and .../nextassembly-of-the-future/proline-cube-filling-station. No 'EcoFill' product name was found on Dürr sources; current names are Somac ProLine Cube, ProLine, Compact X/CompStart, BlueStart, G4 Blue adapters. | REVIEW: GMN10060 (DEXRON-VI) superseded by GMW16444.</t>
         </is>
       </c>
     </row>
